--- a/data/processed/positivacao/2022-08_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-08_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25361,7 +25361,7 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B963" t="inlineStr"/>
@@ -37077,7 +37077,7 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr"/>
@@ -65865,7 +65865,7 @@
     <row r="2522">
       <c r="A2522" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2522" t="inlineStr"/>
@@ -67536,12 +67536,12 @@
       <c r="A2587" t="inlineStr"/>
       <c r="B2587" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 18 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 53.936,52
+          <t>Vendedor 1 - VENDEDOR 01: positivou 18 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 53.936,52
 Vendedor 18 - LOJA: positivou 89 cliente(s), não positivou 758 cliente(s) - Total vendido: R$ 75.579,22
-Vendedor 3 - FERNANDA: positivou 105 cliente(s), não positivou 345 cliente(s) - Total vendido: R$ 130.378,66
-Vendedor 4 - DANIELA: positivou 35 cliente(s), não positivou 615 cliente(s) - Total vendido: R$ 20.027,30
+Vendedor 3 - VENDEDOR 03: positivou 105 cliente(s), não positivou 345 cliente(s) - Total vendido: R$ 130.378,66
+Vendedor 4 - VENDEDOR 04: positivou 35 cliente(s), não positivou 615 cliente(s) - Total vendido: R$ 20.027,30
 Vendedor 5 - SITE: positivou 17 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 3.172,22
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2587" t="inlineStr"/>
